--- a/modelo-resultados.xlsx
+++ b/modelo-resultados.xlsx
@@ -1653,7 +1653,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B4" type="list">
-      <formula1>"Plásticos de Engenharia,Adesivos Estruturais,Pigatto Hub + Licitação,Papel Térmico + Etiquetas,Químicos,Geral (empresa)"</formula1>
+      <formula1>"Plásticos de Engenharia,Adesivos Estruturais,Pigatto Hub + Licitação,Papel Térmico + Etiquetas,Especialidades,Geral (empresa)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
